--- a/analysis/开发人维度/黄雨珊_sku_report.xlsx
+++ b/analysis/开发人维度/黄雨珊_sku_report.xlsx
@@ -716,17 +716,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0H1CX74BH</t>
+          <t>B0H1WW8PDH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2660001</t>
+          <t>2660028</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -750,17 +750,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B0H33HJH8J</t>
+          <t>B0H151GZTB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2660051</t>
+          <t>2660012</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Yangbo-UK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -784,12 +784,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B0H11KZLMX</t>
+          <t>B0H3BBZLVQ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2660015</t>
+          <t>2660080</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -818,17 +818,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B0H1W2JMN7</t>
+          <t>B0H1BVDCTH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2660033</t>
+          <t>2660021</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -852,17 +852,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B0H38Y9CWK</t>
+          <t>B0H2YH7NNR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2660078</t>
+          <t>2660044</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AM-Tyulian-DE</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -886,17 +886,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B0H2DBDCJC</t>
+          <t>B0H1WN812H</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2660035</t>
+          <t>2660031</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -920,7 +920,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B0H14WXP71</t>
+          <t>B0H1CLXYV6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AM-Yangbo-UK</t>
+          <t>AM-Tyulian-DE</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -954,17 +954,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B0H14NZLFN</t>
+          <t>B0H2YZ3QK3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2660010</t>
+          <t>2660060</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AM-Yehao-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -988,17 +988,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B0H33FNFZ1</t>
+          <t>B0H1W2JMN7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2660061</t>
+          <t>2660033</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1022,17 +1022,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0H36HCXQX</t>
+          <t>B0H2Z3LLWH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2660073</t>
+          <t>2660048</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1056,17 +1056,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B0H363GJ6C</t>
+          <t>B0H14WXP71</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2660068</t>
+          <t>2660018</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yangbo-UK</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1090,12 +1090,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B0H14VBH1D</t>
+          <t>B0H2YKLMKX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2660011</t>
+          <t>2660055</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1124,17 +1124,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B0H1W4ZZHY</t>
+          <t>B0H2YM6KRP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2660029</t>
+          <t>2660066</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1158,12 +1158,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0H1W8RRS3</t>
+          <t>B0H2DBDCJC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2660027</t>
+          <t>2660035</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1192,17 +1192,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0H354KKB8</t>
+          <t>B0H11TQDN9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2660072</t>
+          <t>2660013</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1226,17 +1226,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B0H1BSR16Q</t>
+          <t>B0H1CX74BH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2660022</t>
+          <t>2660001</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1260,12 +1260,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B0H2Z8DWY7</t>
+          <t>B0H1W2NCQB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2660054</t>
+          <t>2660026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1294,17 +1294,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0H2YM6KRP</t>
+          <t>B0H2Z56WXJ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2660066</t>
+          <t>2660050</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1328,17 +1328,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0H2YJK1CQ</t>
+          <t>B0H11KZLMX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2660065</t>
+          <t>2660015</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1362,17 +1362,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B0H1W2NCQB</t>
+          <t>B0H2YJK1CQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2660026</t>
+          <t>2660065</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1396,17 +1396,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0H2YZ3QK3</t>
+          <t>B0H1BSR16Q</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2660060</t>
+          <t>2660022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1430,17 +1430,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B0H2VJ5N74</t>
+          <t>B0H2YFL9QD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2660045</t>
+          <t>2660041</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AM-shangchi-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1464,17 +1464,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B0H1G3M883</t>
+          <t>B0H14VBH1D</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2660025</t>
+          <t>2660011</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AM-Yehao-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1498,17 +1498,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B0H11NV8PP</t>
+          <t>B0H2VJ5N74</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2660005</t>
+          <t>2660045</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-shangchi-UK</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1532,17 +1532,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0H2YH3RFP</t>
+          <t>B0H1G3M883</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2660064</t>
+          <t>2660025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yehao-UK</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1566,17 +1566,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B0H1CLXYV6</t>
+          <t>B0H363GJ6C</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2660018</t>
+          <t>2660068</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AM-Tyulian-DE</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1600,17 +1600,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0H3BBZLVQ</t>
+          <t>B0H354KKB8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2660080</t>
+          <t>2660072</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1634,12 +1634,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0H29JPS3J</t>
+          <t>B0H36HCXQX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2660037</t>
+          <t>2660073</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1668,17 +1668,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0H2YH7NNR</t>
+          <t>B0H14XBG9H</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2660044</t>
+          <t>2660004</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yangbo-UK</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1702,17 +1702,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0H39WQ6WB</t>
+          <t>B0H1CP92J4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2660075</t>
+          <t>2660017</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1736,17 +1736,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0H1CPKXFC</t>
+          <t>B0H33HJH8J</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2660014</t>
+          <t>2660051</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1759,23 +1759,23 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
+          <t>欧洲精铺2025</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0H1WW8PDH</t>
+          <t>B0H29JYJ7S</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2660028</t>
+          <t>2660038</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1804,17 +1804,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0H14XBG9H</t>
+          <t>B0H1W83MR3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2660004</t>
+          <t>2660030</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AM-Yangbo-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1838,17 +1838,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0H2YFL9QD</t>
+          <t>B0H39WQ6WB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2660041</t>
+          <t>2660075</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1872,17 +1872,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0H2YKLMKX</t>
+          <t>B0H1W8RRS3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2660055</t>
+          <t>2660027</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1906,17 +1906,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0H151GZTB</t>
+          <t>B0H1W4ZZHY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2660012</t>
+          <t>2660029</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AM-Yangbo-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1940,12 +1940,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0H1BVDCTH</t>
+          <t>B0H2YH3RFP</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2660021</t>
+          <t>2660064</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1974,17 +1974,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0H1WN812H</t>
+          <t>B0H2Z8DWY7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2660031</t>
+          <t>2660054</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2008,30 +2008,30 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0H1CPTG2Q</t>
+          <t>B0H33FNFZ1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2660008</t>
+          <t>2660061</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>15.98</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.37</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2042,17 +2042,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0H2Z3LLWH</t>
+          <t>B0H339FNF3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2660048</t>
+          <t>2660039</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2076,17 +2076,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0H339FNF3</t>
+          <t>B0H14NZLFN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2660039</t>
+          <t>2660010</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Yehao-UK</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2144,30 +2144,30 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0H11TQDN9</t>
+          <t>B0H1CPTG2Q</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2660013</t>
+          <t>2660008</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>15.98</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-2.37</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2178,17 +2178,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0H2Z56WXJ</t>
+          <t>B0H38Y9CWK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2660050</t>
+          <t>2660078</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-DE</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2212,17 +2212,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0H1CP92J4</t>
+          <t>B0H11NV8PP</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2660017</t>
+          <t>2660005</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2246,12 +2246,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0H29JYJ7S</t>
+          <t>B0H29JPS3J</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2660038</t>
+          <t>2660037</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2280,17 +2280,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0H1W83MR3</t>
+          <t>B0H1CPKXFC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2660030</t>
+          <t>2660014</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2303,11 +2303,11 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>欧洲精铺2025</t>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
@@ -2370,17 +2370,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0H3YZZZGJ</t>
+          <t>B0H3LBJVRX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2660093</t>
+          <t>2660088</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AM-Tyulian-DE</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -2404,17 +2404,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B0H3LBJVRX</t>
+          <t>B0H3KJK34C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2660088</t>
+          <t>2660078</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -2438,17 +2438,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B0H3KJK34C</t>
+          <t>B0H3YZZZGJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2660078</t>
+          <t>2660093</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-DE</t>
         </is>
       </c>
       <c r="D4" t="n">

--- a/analysis/开发人维度/黄雨珊_sku_report.xlsx
+++ b/analysis/开发人维度/黄雨珊_sku_report.xlsx
@@ -10,6 +10,7 @@
     <sheet name="汇总" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="26年05月" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="26年06月" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="26年07月" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,70 +447,75 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>总结算销售额</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>总利润率</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>总可用库存</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>存活率</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>存活sku销售量</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>存活sku销售额</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>存活SKU数</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>留存SKU总利润</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>留存SKU利润率</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>淘汰SKU销售量</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>淘汰SKU销售额</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>淘汰SKU总数</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>淘汰率</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>淘汰SKU总利润</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>淘汰SKU利润率</t>
         </is>
@@ -522,67 +528,70 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
+        <v>204</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1529.3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1238.42</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>363</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>95.45%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>178</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1293.06</v>
+      </c>
+      <c r="L2" t="n">
+        <v>42</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-46.64</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-4.48%</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>26</v>
+      </c>
+      <c r="P2" t="n">
+        <v>236.24</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-2.37</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-14.83%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>91</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="K2" t="n">
-        <v>47</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-2.37</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-14.83%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>4.55%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>26.87%</t>
         </is>
       </c>
     </row>
@@ -593,65 +602,142 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>14.57</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
+        <v>-8.77</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-60.19%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>721</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="L3" t="n">
+        <v>87</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-8.77</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>-60.19%</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="F4" t="n">
+        <v>83.22</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>10.19%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="J4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="L4" t="n">
+        <v>17</v>
+      </c>
+      <c r="M4" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>10.19%</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
@@ -668,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,10 +790,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>总结算销售额</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>总可用库存</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>最新标签</t>
         </is>
@@ -716,12 +807,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0H1WW8PDH</t>
+          <t>B0H2YFL9QD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2660028</t>
+          <t>2660041</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -730,18 +821,21 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>35.89</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-18.24</v>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>35.89</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -750,32 +844,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B0H151GZTB</t>
+          <t>B0H2DBDCJC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2660012</t>
+          <t>2660035</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AM-Yangbo-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>17.57</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>7.476076555023924</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -784,32 +881,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B0H3BBZLVQ</t>
+          <t>B0H2YH3RFP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2660080</t>
+          <t>2660064</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>33.31</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>33.31</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -818,17 +918,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B0H1BVDCTH</t>
+          <t>B0H14XBG9H</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2660021</t>
+          <t>2660004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yangbo-UK</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -838,46 +938,52 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>欧洲精铺2025</t>
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B0H2YH7NNR</t>
+          <t>B0H11NV8PP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2660044</t>
+          <t>2660005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>29.12</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>29.12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -886,17 +992,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B0H1WN812H</t>
+          <t>B0H1CP92J4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2660031</t>
+          <t>2660017</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -911,7 +1017,10 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -920,34 +1029,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B0H1CLXYV6</t>
+          <t>B0H151GZTB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2660018</t>
+          <t>2660012</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AM-Tyulian-DE</t>
+          <t>AM-Yangbo-UK</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>20.94</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>欧洲精铺2025</t>
+        <v>11.6751269035533</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
@@ -968,18 +1080,21 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>22.74</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-13.99</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>22.74</v>
+      </c>
+      <c r="H9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -988,32 +1103,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B0H1W2JMN7</t>
+          <t>B0H33HJH8J</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2660033</t>
+          <t>2660051</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>5.99</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1022,32 +1140,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0H2Z3LLWH</t>
+          <t>B0H339FNF3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2660048</t>
+          <t>2660039</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>27.66</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-7.27</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>27.66</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1056,32 +1177,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B0H14WXP71</t>
+          <t>B0H1W8RRS3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2660018</t>
+          <t>2660027</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AM-Yangbo-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>151.62</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="G12" t="n">
-        <v>15</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>99.8158379373849</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1090,32 +1214,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B0H2YKLMKX</t>
+          <t>B0H2Z8DWY7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2660055</t>
+          <t>2660054</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>13.73</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-8.52</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>13.73</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1124,17 +1251,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B0H2YM6KRP</t>
+          <t>B0H354KKB8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2660066</t>
+          <t>2660072</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1144,12 +1271,15 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-2.19</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1158,17 +1288,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0H2DBDCJC</t>
+          <t>B0H33FNFZ1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2660035</t>
+          <t>2660061</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1178,12 +1308,15 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-1.15</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1192,32 +1325,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0H11TQDN9</t>
+          <t>B0H1WN812H</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2660013</t>
+          <t>2660031</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>119.8</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>21.65</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>99.81558321807283</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1226,17 +1362,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B0H1CX74BH</t>
+          <t>B0H3BBZLVQ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2660001</t>
+          <t>2660080</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1251,7 +1387,10 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1260,32 +1399,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B0H1W2NCQB</t>
+          <t>B0H1W4ZZHY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2660026</t>
+          <t>2660029</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>39.96</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>39.96</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1294,17 +1436,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0H2Z56WXJ</t>
+          <t>B0H2YM6KRP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2660050</t>
+          <t>2660066</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1319,7 +1461,10 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1328,17 +1473,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0H11KZLMX</t>
+          <t>B0H1CX74BH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2660015</t>
+          <t>2660001</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1353,7 +1498,10 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1362,32 +1510,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B0H2YJK1CQ</t>
+          <t>B0H1W2JMN7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2660065</t>
+          <t>2660033</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>26.1</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-7.58</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>26.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1396,17 +1547,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0H1BSR16Q</t>
+          <t>B0H39WQ6WB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2660022</t>
+          <t>2660075</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1416,12 +1567,15 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1430,12 +1584,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B0H2YFL9QD</t>
+          <t>B0H363GJ6C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2660041</t>
+          <t>2660068</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1455,7 +1609,10 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1464,17 +1621,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B0H14VBH1D</t>
+          <t>B0H1CPKXFC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2660011</t>
+          <t>2660014</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1489,41 +1646,47 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>欧洲精铺2025</t>
+      <c r="H24" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B0H2VJ5N74</t>
+          <t>B0H29JPS3J</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2660045</t>
+          <t>2660037</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AM-shangchi-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>119.85</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>21.62</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr">
+        <v>93.22984044846916</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1532,32 +1695,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0H1G3M883</t>
+          <t>B0H11TQDN9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2660025</t>
+          <t>2660013</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AM-Yehao-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>13.98</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr">
+        <v>11.5702479338843</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8</v>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1566,12 +1732,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B0H363GJ6C</t>
+          <t>B0H2YJK1CQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2660068</t>
+          <t>2660065</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1580,18 +1746,21 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>13.98</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-1.59</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr">
+        <v>13.98</v>
+      </c>
+      <c r="H27" t="n">
+        <v>13</v>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1600,12 +1769,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0H354KKB8</t>
+          <t>B0H1CPTG2Q</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2660072</t>
+          <t>2660008</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1614,32 +1783,35 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>87.89</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>12.81</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>欧洲精铺2025</t>
+        <v>73.2418524871355</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025淘汰</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0H36HCXQX</t>
+          <t>B0H29JYJ7S</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2660073</t>
+          <t>2660038</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1659,7 +1831,10 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1668,17 +1843,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0H14XBG9H</t>
+          <t>B0H1BSR16Q</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2660004</t>
+          <t>2660022</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AM-Yangbo-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1693,7 +1868,10 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1702,17 +1880,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0H1CP92J4</t>
+          <t>B0H2YKLMKX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2660017</t>
+          <t>2660055</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1727,7 +1905,10 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1736,12 +1917,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0H33HJH8J</t>
+          <t>B0H33H1GBX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2660051</t>
+          <t>2660062</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1750,18 +1931,21 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>13.98</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-2.51</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="inlineStr">
+        <v>13.98</v>
+      </c>
+      <c r="H32" t="n">
+        <v>8</v>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1770,32 +1954,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0H29JYJ7S</t>
+          <t>B0H11KZLMX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2660038</t>
+          <t>2660015</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yujinbing-UK</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>7.99</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr">
+        <v>49.90630855715177</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1804,17 +1991,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0H1W83MR3</t>
+          <t>B0H38Y9CWK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2660030</t>
+          <t>2660078</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Tyulian-DE</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1824,12 +2011,15 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-4.05</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" t="n">
+        <v>20</v>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1838,66 +2028,72 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0H39WQ6WB</t>
+          <t>B0H2VJ5N74</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2660075</t>
+          <t>2660045</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AM-Yujinbing-UK</t>
+          <t>AM-shangchi-UK</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-1.84</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>欧洲精铺2025</t>
+        <v>6.58</v>
+      </c>
+      <c r="H35" t="n">
+        <v>14</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0H1W8RRS3</t>
+          <t>B0H36HCXQX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2660027</t>
+          <t>2660073</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>95.88</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="inlineStr">
+        <v>19.96887966804979</v>
+      </c>
+      <c r="H36" t="n">
+        <v>8</v>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1906,17 +2102,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0H1W4ZZHY</t>
+          <t>B0H2Z3LLWH</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2660029</t>
+          <t>2660048</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1931,7 +2127,10 @@
       <c r="G37" t="n">
         <v>0</v>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" t="n">
+        <v>15</v>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1940,12 +2139,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0H2YH3RFP</t>
+          <t>B0H14VBH1D</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2660064</t>
+          <t>2660011</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1954,18 +2153,21 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>7.99</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>-27.83</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr">
+        <v>7.99</v>
+      </c>
+      <c r="H38" t="n">
+        <v>9</v>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -1974,51 +2176,54 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0H2Z8DWY7</t>
+          <t>B0H14WXP71</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2660054</t>
+          <t>2660018</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Yangbo-UK</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>148.35</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>40.09</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>欧洲精铺2025</t>
+        <v>123.6201048411964</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025淘汰</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0H33FNFZ1</t>
+          <t>B0H2YH7NNR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2660061</t>
+          <t>2660044</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2028,46 +2233,52 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>欧洲精铺2025</t>
+      <c r="H40" t="n">
+        <v>15</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0H339FNF3</t>
+          <t>B0H1WW8PDH</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2660039</t>
+          <t>2660028</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>96.98</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>24.82</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr">
+        <v>81.51067323481116</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -2076,32 +2287,35 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0H14NZLFN</t>
+          <t>B0H1W83MR3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2660010</t>
+          <t>2660030</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AM-Yehao-UK</t>
+          <t>AM-Liuhu-UK</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>-8.73</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr">
+        <v>95.98999999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -2110,17 +2324,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0H33H1GBX</t>
+          <t>B0H2Z56WXJ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2660062</t>
+          <t>2660050</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AM-Liuhu-UK</t>
+          <t>AM-Yulu-UK</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2130,12 +2344,15 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" t="n">
+        <v>10</v>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -2144,32 +2361,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0H1CPTG2Q</t>
+          <t>B0H1CLXYV6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2660008</t>
+          <t>2660018</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-DE</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E44" t="n">
-        <v>15.98</v>
+        <v>193.57</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.37</v>
+        <v>-3.87</v>
       </c>
       <c r="G44" t="n">
-        <v>17</v>
-      </c>
-      <c r="H44" t="inlineStr">
+        <v>193.57</v>
+      </c>
+      <c r="H44" t="n">
+        <v>42</v>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -2178,17 +2398,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0H38Y9CWK</t>
+          <t>B0H1BVDCTH</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2660078</t>
+          <t>2660021</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AM-Tyulian-DE</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2198,116 +2418,17 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-5.61</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>欧洲精铺2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>B0H11NV8PP</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2660005</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AM-Yujinbing-UK</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>欧洲精铺2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>B0H29JPS3J</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2660037</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AM-Tyulian-UK</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>欧洲精铺2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>B0H1CPKXFC</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2660014</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AM-Yulu-UK</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>10</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>欧洲精铺2025,欧洲精铺2025非标品</t>
+      <c r="H45" t="n">
+        <v>20</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2358,10 +2479,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>总结算销售额</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>总可用库存</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>最新标签</t>
         </is>
@@ -2370,17 +2496,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0H3LBJVRX</t>
+          <t>B0H14NZLFN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2660088</t>
+          <t>2660010</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AM-Tyulian-UK</t>
+          <t>AM-Yehao-UK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -2390,12 +2516,15 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -2404,17 +2533,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B0H3KJK34C</t>
+          <t>B0H6FXH52J</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2660078</t>
+          <t>2660178</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AM-Yulu-UK</t>
+          <t>AM-Tyulian-UK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -2429,7 +2558,10 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -2458,12 +2590,15 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0.16</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -2472,32 +2607,3796 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>B0H6WGCPDJ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2660204</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B0H4LGB5WP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2660100</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B0H6G1HXRC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2660173</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B0H6M8RL5X</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2660194</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AM-GC-UK</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B0H459FDYK</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2660089</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B0H6WR7GMY</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2660215</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>B0H4R18H7Q</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2660131</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>20</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B0H5BY787N</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2660144</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B0H4QML93S</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2660114</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B0H5BVH5YD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2660134</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B0H6MCMGMM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2660200</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B0H45G8ZN6</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2660096</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>14</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B0H6WY34CV</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2660219</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B0H5VPNX76</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2660152</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B0H4QN7KYZ</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2660125</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>15</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>B0H1G3M883</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2660025</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AM-Yehao-UK</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-3.72</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="H20" t="n">
+        <v>19</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B0H4QQ6NHP</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2660129</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>21</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>B0H3TN4Y5B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2660090</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>15</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>B0H6MKJTCB</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2660196</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AM-Liuhu-UK</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>B0H6MGYC6Q</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2660195</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AM-GC-UK</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>B0H5QJNN48</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2660159</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B0H4QVTLC3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2660111</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>20</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B0H4T2K981</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2660123</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>25</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B0H6FTZ7XS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2660184</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>15</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>B0H5VTDM87</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2660159</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>B0H6BFMHDL</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2660169</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>15</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>B0H5JQLCC2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2660161</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>15</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>B0H5BGHYBX</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2660141</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>B0H6PPX7W2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2660200</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>B0H6MHYD3V</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2660201</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AM-Liuhu-UK</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>B0H6X99F6G</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2660220</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AM-Liuhu-UK</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>B0H5C6H4L8</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2660148</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>10</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>B0H4PZ684C</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2660101</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>10</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>B0H5BSHHNV</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2660143</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>B0H5BVMGBX</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2660147</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>10</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>B0H6X4YPK1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2660210</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>B0H6FQDP5K</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2660177</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>20</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>B0H5VNFD7C</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2660158</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>B0H4SQLYB4</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2660116</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>B0H3LBJVRX</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2660088</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>15</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>B0H4QXC36K</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2660119</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>B0H4FT2Z9N</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2660110</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AM-shangchi-UK</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>10</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>B0H5C2BKX2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2660139</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>B0H6WT1RCT</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2660203</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>B0H6ZPNK42</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2660208</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>B0H6ZD6CB6</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2660205</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>B0H6M9CVM3</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2660193</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AM-Liuhu-UK</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>B0H6FN4M5Q</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2660189</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>20</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>B0H6M8KH7N</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2660190</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>B0H5C2J4NH</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2660135</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>10</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>B0H3TP11Q7</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2660097</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>10</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>B0H5J7N1VL</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2660146</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>B0H4QTVVR4</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2660113</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>10</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>B0H5VT7YRC</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2660166</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>B0H6G7HRH9</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2660171</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AM-Liuhu-UK</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>B0H6X6SNQ2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2660233</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>B0H4TJG3RR</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2660115</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>B0H6MFW34G</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2660195</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>B0H6X4CMWX</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2660237</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AM-GC-UK</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>B0H5VQG42X</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2660156</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>B0H459Z6Q1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2660093</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AM-Liuhu-UK</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>10</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>B0H6ZJFSMB</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2660207</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>B0H5QFD6RP</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2660167</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>15</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>B0H45FB3HG</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2660099</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>8</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>B0H6XFR6NW</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2660228</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AM-Liuhu-UK</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>B0H4SXNRYL</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2660122</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>B0H45CT38G</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2660095</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>15</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>B0H6M5HG9K</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2660191</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>B0H5JP8V6M</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2660163</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>15</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>B0H6M6CDV4</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2660192</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>B0H5TSQPMB</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2660166</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AM-Pyongqian-DE</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>B0H5VJR93K</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2660150</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>B0H6X26DDW</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2660216</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>B0H5Q8VGVC</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2660168</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AM-Yujinbing-UK</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>B0H5QF3F5P</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2660161</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>20</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>B0H4LDNF3Y</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2660107</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>15</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>B0H6MB6RCN</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2660197</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>B0H5BTQ8FG</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2660142</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>20</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>B0H6WX9MTB</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2660202</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>B0H4FXMTRH</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2660102</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AM-Liuhu-UK</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>15</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>B0H3KNJDG7</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2660079</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="G85" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H85" t="n">
+        <v>9</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>B0H4PVGNQH</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2660106</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>15</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>B0H6ZSQJ2W</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2660206</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>B0H6FQHWY9</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2660172</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>10</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ASIN</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>店铺</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>总销量</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>总结算利润</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>总结算销售额</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>总可用库存</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>最新标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B0H7RTGDJD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2660247</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B0H7RPY311</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2660239</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B0H7RK9RXT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2660249</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B0H7RHFJT1</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2660079</t>
+          <t>2660242</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B0H3KJK34C</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2660078</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>AM-Yulu-UK</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B0H7RVTVFB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2660243</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B0H73Z7C38</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2660223</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B0H7VTQJ2X</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2660244</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B0H1W2NCQB</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2660026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>83.22211630123927</v>
+      </c>
+      <c r="H10" t="n">
+        <v>20</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>B0H7VP5BDD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2660248</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B0H7RJPF4N</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2660245</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AM-Yulu-UK</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B0H7S5GZ4W</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2660261</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AM-Pyongqian-UK</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B0H73ZBSX3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2660224</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B0H7RSR1BS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2660238</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-DE</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B0H7S1NLFW</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2660250</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AM-Liuhu-UK</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B0H7W8HBXQ</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2660246</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B0H74558GC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2660227</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AM-Tyulian-UK</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
